--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746991</v>
+        <v>122746999</v>
       </c>
       <c r="B7" t="n">
-        <v>91507</v>
+        <v>79843</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559141</v>
+        <v>559026</v>
       </c>
       <c r="R7" t="n">
-        <v>6902206</v>
+        <v>6902288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,17 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746999</v>
+        <v>122746991</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>91507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559026</v>
+        <v>559141</v>
       </c>
       <c r="R8" t="n">
-        <v>6902288</v>
+        <v>6902206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1381,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746993</v>
+        <v>122746996</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>79807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559025</v>
+        <v>559150</v>
       </c>
       <c r="R2" t="n">
-        <v>6902245</v>
+        <v>6902212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746996</v>
+        <v>122746998</v>
       </c>
       <c r="B3" t="n">
-        <v>79803</v>
+        <v>79807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559150</v>
+        <v>559064</v>
       </c>
       <c r="R3" t="n">
-        <v>6902212</v>
+        <v>6902199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746995</v>
+        <v>122746993</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559147</v>
+        <v>559025</v>
       </c>
       <c r="R4" t="n">
-        <v>6902216</v>
+        <v>6902245</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746992</v>
+        <v>122746999</v>
       </c>
       <c r="B5" t="n">
-        <v>91385</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559033</v>
+        <v>559026</v>
       </c>
       <c r="R5" t="n">
-        <v>6902278</v>
+        <v>6902288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746997</v>
+        <v>122746992</v>
       </c>
       <c r="B6" t="n">
-        <v>79843</v>
+        <v>91389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559148</v>
+        <v>559033</v>
       </c>
       <c r="R6" t="n">
-        <v>6902210</v>
+        <v>6902278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746999</v>
+        <v>122746991</v>
       </c>
       <c r="B7" t="n">
-        <v>79843</v>
+        <v>91511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559026</v>
+        <v>559141</v>
       </c>
       <c r="R7" t="n">
-        <v>6902288</v>
+        <v>6902206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746991</v>
+        <v>122746997</v>
       </c>
       <c r="B8" t="n">
-        <v>91507</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559141</v>
+        <v>559148</v>
       </c>
       <c r="R8" t="n">
-        <v>6902206</v>
+        <v>6902210</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,17 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746998</v>
+        <v>122746995</v>
       </c>
       <c r="B9" t="n">
-        <v>79803</v>
+        <v>79022</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,34 +1438,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559064</v>
+        <v>559147</v>
       </c>
       <c r="R9" t="n">
-        <v>6902199</v>
+        <v>6902216</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746996</v>
+        <v>122746999</v>
       </c>
       <c r="B2" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559150</v>
+        <v>559026</v>
       </c>
       <c r="R2" t="n">
-        <v>6902212</v>
+        <v>6902288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746998</v>
+        <v>122746996</v>
       </c>
       <c r="B3" t="n">
         <v>79807</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559064</v>
+        <v>559150</v>
       </c>
       <c r="R3" t="n">
-        <v>6902199</v>
+        <v>6902212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746993</v>
+        <v>122746997</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559025</v>
+        <v>559148</v>
       </c>
       <c r="R4" t="n">
-        <v>6902245</v>
+        <v>6902210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746999</v>
+        <v>122746995</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559026</v>
+        <v>559147</v>
       </c>
       <c r="R5" t="n">
-        <v>6902288</v>
+        <v>6902216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746992</v>
+        <v>122746991</v>
       </c>
       <c r="B6" t="n">
-        <v>91389</v>
+        <v>91511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559033</v>
+        <v>559141</v>
       </c>
       <c r="R6" t="n">
-        <v>6902278</v>
+        <v>6902206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1169,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746991</v>
+        <v>122746998</v>
       </c>
       <c r="B7" t="n">
-        <v>91511</v>
+        <v>79807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559141</v>
+        <v>559064</v>
       </c>
       <c r="R7" t="n">
-        <v>6902206</v>
+        <v>6902199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,17 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746997</v>
+        <v>122746993</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,34 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559148</v>
+        <v>559025</v>
       </c>
       <c r="R8" t="n">
-        <v>6902210</v>
+        <v>6902245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746995</v>
+        <v>122746992</v>
       </c>
       <c r="B9" t="n">
-        <v>79022</v>
+        <v>91389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559147</v>
+        <v>559033</v>
       </c>
       <c r="R9" t="n">
-        <v>6902216</v>
+        <v>6902278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746999</v>
+        <v>122746995</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559026</v>
+        <v>559147</v>
       </c>
       <c r="R2" t="n">
-        <v>6902288</v>
+        <v>6902216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746997</v>
+        <v>122746998</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559148</v>
+        <v>559064</v>
       </c>
       <c r="R4" t="n">
-        <v>6902210</v>
+        <v>6902199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746995</v>
+        <v>122746997</v>
       </c>
       <c r="B5" t="n">
-        <v>79022</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559147</v>
+        <v>559148</v>
       </c>
       <c r="R5" t="n">
-        <v>6902216</v>
+        <v>6902210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746991</v>
+        <v>122746992</v>
       </c>
       <c r="B6" t="n">
-        <v>91511</v>
+        <v>91389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559141</v>
+        <v>559033</v>
       </c>
       <c r="R6" t="n">
-        <v>6902206</v>
+        <v>6902278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,17 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746998</v>
+        <v>122746993</v>
       </c>
       <c r="B7" t="n">
-        <v>79807</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559064</v>
+        <v>559025</v>
       </c>
       <c r="R7" t="n">
-        <v>6902199</v>
+        <v>6902245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,12 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746993</v>
+        <v>122746991</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>91511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559025</v>
+        <v>559141</v>
       </c>
       <c r="R8" t="n">
-        <v>6902245</v>
+        <v>6902206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1381,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746992</v>
+        <v>122746999</v>
       </c>
       <c r="B9" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559033</v>
+        <v>559026</v>
       </c>
       <c r="R9" t="n">
-        <v>6902278</v>
+        <v>6902288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746995</v>
+        <v>122746996</v>
       </c>
       <c r="B2" t="n">
-        <v>79022</v>
+        <v>79807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559147</v>
+        <v>559150</v>
       </c>
       <c r="R2" t="n">
-        <v>6902216</v>
+        <v>6902212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746996</v>
+        <v>122746999</v>
       </c>
       <c r="B3" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559150</v>
+        <v>559026</v>
       </c>
       <c r="R3" t="n">
-        <v>6902212</v>
+        <v>6902288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746998</v>
+        <v>122746995</v>
       </c>
       <c r="B4" t="n">
-        <v>79807</v>
+        <v>79022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6459</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559064</v>
+        <v>559147</v>
       </c>
       <c r="R4" t="n">
-        <v>6902199</v>
+        <v>6902216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746997</v>
+        <v>122746992</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>91389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559148</v>
+        <v>559033</v>
       </c>
       <c r="R5" t="n">
-        <v>6902210</v>
+        <v>6902278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746992</v>
+        <v>122746997</v>
       </c>
       <c r="B6" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559033</v>
+        <v>559148</v>
       </c>
       <c r="R6" t="n">
-        <v>6902278</v>
+        <v>6902210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746993</v>
+        <v>122746991</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>91511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559025</v>
+        <v>559141</v>
       </c>
       <c r="R7" t="n">
-        <v>6902245</v>
+        <v>6902206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746991</v>
+        <v>122746993</v>
       </c>
       <c r="B8" t="n">
-        <v>91511</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559141</v>
+        <v>559025</v>
       </c>
       <c r="R8" t="n">
-        <v>6902206</v>
+        <v>6902245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,17 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746999</v>
+        <v>122746998</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559026</v>
+        <v>559064</v>
       </c>
       <c r="R9" t="n">
-        <v>6902288</v>
+        <v>6902199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746996</v>
+        <v>122746992</v>
       </c>
       <c r="B2" t="n">
-        <v>79807</v>
+        <v>91397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559150</v>
+        <v>559033</v>
       </c>
       <c r="R2" t="n">
-        <v>6902212</v>
+        <v>6902278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746999</v>
+        <v>122746995</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559026</v>
+        <v>559147</v>
       </c>
       <c r="R3" t="n">
-        <v>6902288</v>
+        <v>6902216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746995</v>
+        <v>122746998</v>
       </c>
       <c r="B4" t="n">
-        <v>79022</v>
+        <v>79807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559147</v>
+        <v>559064</v>
       </c>
       <c r="R4" t="n">
-        <v>6902216</v>
+        <v>6902199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746992</v>
+        <v>122746996</v>
       </c>
       <c r="B5" t="n">
-        <v>91389</v>
+        <v>79807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559033</v>
+        <v>559150</v>
       </c>
       <c r="R5" t="n">
-        <v>6902278</v>
+        <v>6902212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746991</v>
+        <v>122746993</v>
       </c>
       <c r="B7" t="n">
-        <v>91511</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559141</v>
+        <v>559025</v>
       </c>
       <c r="R7" t="n">
-        <v>6902206</v>
+        <v>6902245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,17 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746993</v>
+        <v>122746991</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>91519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559025</v>
+        <v>559141</v>
       </c>
       <c r="R8" t="n">
-        <v>6902245</v>
+        <v>6902206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1381,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746998</v>
+        <v>122746999</v>
       </c>
       <c r="B9" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559064</v>
+        <v>559026</v>
       </c>
       <c r="R9" t="n">
-        <v>6902199</v>
+        <v>6902288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746996</v>
+        <v>122746997</v>
       </c>
       <c r="B5" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559150</v>
+        <v>559148</v>
       </c>
       <c r="R5" t="n">
-        <v>6902212</v>
+        <v>6902210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746997</v>
+        <v>122746996</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559148</v>
+        <v>559150</v>
       </c>
       <c r="R6" t="n">
-        <v>6902210</v>
+        <v>6902212</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746992</v>
+        <v>122746997</v>
       </c>
       <c r="B2" t="n">
-        <v>91397</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559033</v>
+        <v>559148</v>
       </c>
       <c r="R2" t="n">
-        <v>6902278</v>
+        <v>6902210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746998</v>
+        <v>122746996</v>
       </c>
       <c r="B4" t="n">
         <v>79807</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559064</v>
+        <v>559150</v>
       </c>
       <c r="R4" t="n">
-        <v>6902199</v>
+        <v>6902212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746997</v>
+        <v>122746993</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559148</v>
+        <v>559025</v>
       </c>
       <c r="R5" t="n">
-        <v>6902210</v>
+        <v>6902245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746996</v>
+        <v>122746999</v>
       </c>
       <c r="B6" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559150</v>
+        <v>559026</v>
       </c>
       <c r="R6" t="n">
-        <v>6902212</v>
+        <v>6902288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746993</v>
+        <v>122746991</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>91519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559025</v>
+        <v>559141</v>
       </c>
       <c r="R7" t="n">
-        <v>6902245</v>
+        <v>6902206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746991</v>
+        <v>122746998</v>
       </c>
       <c r="B8" t="n">
-        <v>91519</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559141</v>
+        <v>559064</v>
       </c>
       <c r="R8" t="n">
-        <v>6902206</v>
+        <v>6902199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,17 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746999</v>
+        <v>122746992</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>91397</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559026</v>
+        <v>559033</v>
       </c>
       <c r="R9" t="n">
-        <v>6902288</v>
+        <v>6902278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746997</v>
+        <v>122746996</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559148</v>
+        <v>559150</v>
       </c>
       <c r="R2" t="n">
-        <v>6902210</v>
+        <v>6902212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746996</v>
+        <v>122746992</v>
       </c>
       <c r="B4" t="n">
-        <v>79807</v>
+        <v>91397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559150</v>
+        <v>559033</v>
       </c>
       <c r="R4" t="n">
-        <v>6902212</v>
+        <v>6902278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746993</v>
+        <v>122746998</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>79807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559025</v>
+        <v>559064</v>
       </c>
       <c r="R5" t="n">
-        <v>6902245</v>
+        <v>6902199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746999</v>
+        <v>122746997</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559026</v>
+        <v>559148</v>
       </c>
       <c r="R6" t="n">
-        <v>6902288</v>
+        <v>6902210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746991</v>
+        <v>122746993</v>
       </c>
       <c r="B7" t="n">
-        <v>91519</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559141</v>
+        <v>559025</v>
       </c>
       <c r="R7" t="n">
-        <v>6902206</v>
+        <v>6902245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,17 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746998</v>
+        <v>122746991</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>91519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559064</v>
+        <v>559141</v>
       </c>
       <c r="R8" t="n">
-        <v>6902199</v>
+        <v>6902206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1381,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746992</v>
+        <v>122746999</v>
       </c>
       <c r="B9" t="n">
-        <v>91397</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559033</v>
+        <v>559026</v>
       </c>
       <c r="R9" t="n">
-        <v>6902278</v>
+        <v>6902288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746996</v>
+        <v>122746995</v>
       </c>
       <c r="B2" t="n">
-        <v>79807</v>
+        <v>79022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6459</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559150</v>
+        <v>559147</v>
       </c>
       <c r="R2" t="n">
-        <v>6902212</v>
+        <v>6902216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746995</v>
+        <v>122746992</v>
       </c>
       <c r="B3" t="n">
-        <v>79022</v>
+        <v>91397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6459</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559147</v>
+        <v>559033</v>
       </c>
       <c r="R3" t="n">
-        <v>6902216</v>
+        <v>6902278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746992</v>
+        <v>122746998</v>
       </c>
       <c r="B4" t="n">
-        <v>91397</v>
+        <v>79807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559033</v>
+        <v>559064</v>
       </c>
       <c r="R4" t="n">
-        <v>6902278</v>
+        <v>6902199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746998</v>
+        <v>122746996</v>
       </c>
       <c r="B5" t="n">
         <v>79807</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559064</v>
+        <v>559150</v>
       </c>
       <c r="R5" t="n">
-        <v>6902199</v>
+        <v>6902212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746997</v>
+        <v>122746993</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559148</v>
+        <v>559025</v>
       </c>
       <c r="R6" t="n">
-        <v>6902210</v>
+        <v>6902245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746993</v>
+        <v>122746997</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559025</v>
+        <v>559148</v>
       </c>
       <c r="R7" t="n">
-        <v>6902245</v>
+        <v>6902210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746991</v>
+        <v>122746999</v>
       </c>
       <c r="B8" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559141</v>
+        <v>559026</v>
       </c>
       <c r="R8" t="n">
-        <v>6902206</v>
+        <v>6902288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,17 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746999</v>
+        <v>122746991</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559026</v>
+        <v>559141</v>
       </c>
       <c r="R9" t="n">
-        <v>6902288</v>
+        <v>6902206</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1487,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746995</v>
+        <v>122746998</v>
       </c>
       <c r="B2" t="n">
-        <v>79022</v>
+        <v>79810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559147</v>
+        <v>559064</v>
       </c>
       <c r="R2" t="n">
-        <v>6902216</v>
+        <v>6902199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122746992</v>
       </c>
       <c r="B3" t="n">
-        <v>91397</v>
+        <v>91400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746998</v>
+        <v>122746999</v>
       </c>
       <c r="B4" t="n">
-        <v>79807</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559064</v>
+        <v>559026</v>
       </c>
       <c r="R4" t="n">
-        <v>6902199</v>
+        <v>6902288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746996</v>
+        <v>122746993</v>
       </c>
       <c r="B5" t="n">
-        <v>79807</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559150</v>
+        <v>559025</v>
       </c>
       <c r="R5" t="n">
-        <v>6902212</v>
+        <v>6902245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746993</v>
+        <v>122746996</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>79810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559025</v>
+        <v>559150</v>
       </c>
       <c r="R6" t="n">
-        <v>6902245</v>
+        <v>6902212</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>122746997</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746999</v>
+        <v>122746991</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>91522</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559026</v>
+        <v>559141</v>
       </c>
       <c r="R8" t="n">
-        <v>6902288</v>
+        <v>6902206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,12 +1381,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746991</v>
+        <v>122746995</v>
       </c>
       <c r="B9" t="n">
-        <v>91519</v>
+        <v>79025</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559141</v>
+        <v>559147</v>
       </c>
       <c r="R9" t="n">
-        <v>6902206</v>
+        <v>6902216</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,17 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47624-2024 artfynd.xlsx
+++ b/artfynd/A 47624-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122746998</v>
       </c>
       <c r="B2" t="n">
-        <v>79810</v>
+        <v>79812</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122746992</v>
       </c>
       <c r="B3" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746999</v>
+        <v>122746997</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brattflögan N, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559026</v>
+        <v>559148</v>
       </c>
       <c r="R4" t="n">
-        <v>6902288</v>
+        <v>6902210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122746993</v>
+        <v>122746991</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>91524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Grytberget NV, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559025</v>
+        <v>559141</v>
       </c>
       <c r="R5" t="n">
-        <v>6902245</v>
+        <v>6902206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På klen låga av sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122746996</v>
+        <v>122746993</v>
       </c>
       <c r="B6" t="n">
-        <v>79810</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559150</v>
+        <v>559025</v>
       </c>
       <c r="R6" t="n">
-        <v>6902212</v>
+        <v>6902245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122746997</v>
+        <v>122746995</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>79027</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråten SV, Mpd</t>
+          <t>Bråta göl NV, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559148</v>
+        <v>559147</v>
       </c>
       <c r="R7" t="n">
-        <v>6902210</v>
+        <v>6902216</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122746991</v>
+        <v>122746999</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grytberget NV, Mpd</t>
+          <t>Brattflögan N, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559141</v>
+        <v>559026</v>
       </c>
       <c r="R8" t="n">
-        <v>6902206</v>
+        <v>6902288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,17 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klen låga av sälg</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122746995</v>
+        <v>122746996</v>
       </c>
       <c r="B9" t="n">
-        <v>79025</v>
+        <v>79812</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,34 +1438,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråta göl NV, Mpd</t>
+          <t>Bråten SV, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559147</v>
+        <v>559150</v>
       </c>
       <c r="R9" t="n">
-        <v>6902216</v>
+        <v>6902212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
